--- a/dtw-it-center-pm-toolkit/templates/PM_Toolkit_02_Workbook_TEMPLATE.xlsx
+++ b/dtw-it-center-pm-toolkit/templates/PM_Toolkit_02_Workbook_TEMPLATE.xlsx
@@ -11,11 +11,12 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="WBS_Schedule" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Budget_Tracker" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="RACI_Matrix" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Stakeholder_Register" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Risk_Register" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Issue_Change_Log" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Vendor_Contractor_Register" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Quality_Checklist" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="RACI_Matrix" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Stakeholder_Register" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Risk_Register" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Issue_Change_Log" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Vendor_Contractor_Register" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="120">
   <si>
     <t xml:space="preserve">[Project Name] — PM Toolkit (Template) — PM Tracking Workbook</t>
   </si>
@@ -164,6 +165,39 @@
     <t xml:space="preserve">TOTAL</t>
   </si>
   <si>
+    <t xml:space="preserve">Quality Control Checklist  (deliverable/checkpoint acceptance tracking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceptance Criteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inspection Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Checkpoint 1 — e.g., an inspection or acceptance test]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Category]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Acceptance criteria]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Inspection/test method]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Checkpoint 2]</t>
+  </si>
+  <si>
     <t xml:space="preserve">RACI Matrix  (R = Responsible · A = Accountable · C = Consulted · I = Informed)</t>
   </si>
   <si>
@@ -251,9 +285,6 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
     <t xml:space="preserve">Probability (1-5)</t>
   </si>
   <si>
@@ -270,9 +301,6 @@
   </si>
   <si>
     <t xml:space="preserve">[Risk description]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Category]</t>
   </si>
   <si>
     <t xml:space="preserve">[Response strategy]</t>
@@ -1300,11 +1328,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1316,70 +1349,80 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
       <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="F2" s="9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
+      <c r="G2" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>53</v>
+      <c r="E3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>55</v>
-      </c>
       <c r="E4" s="11" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>53</v>
+        <v>24</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1399,16 +1442,13 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1418,62 +1458,62 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="9" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="B3" s="12" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="C3" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="D3" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="E3" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>69</v>
+      <c r="F3" s="12" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>65</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>70</v>
-      </c>
       <c r="E4" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1491,6 +1531,105 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1511,7 +1650,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1524,25 +1663,25 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H2" s="9" t="s">
         <v>13</v>
@@ -1553,13 +1692,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D3" s="10" t="n">
         <v>3</v>
@@ -1572,24 +1711,24 @@
         <v>12</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H3" s="10" t="s">
         <v>23</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>2</v>
@@ -1602,13 +1741,13 @@
         <v>6</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>23</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1645,7 +1784,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1657,39 +1796,39 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>18</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>24</v>
@@ -1698,24 +1837,24 @@
         <v>23</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>24</v>
@@ -1724,13 +1863,13 @@
         <v>23</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1747,7 +1886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1765,7 +1904,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1776,13 +1915,13 @@
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>14</v>
@@ -1791,18 +1930,18 @@
         <v>15</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C3" s="13" t="n">
         <v>0</v>
@@ -1814,10 +1953,10 @@
         <v>24</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
